--- a/file/XLK-227-A7SignalStrength.xlsx
+++ b/file/XLK-227-A7SignalStrength.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B0FE57-FD8D-1447-9EAB-8DFF5210A101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62220CF8-4248-3043-A133-21844D2C5CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6220" yWindow="500" windowWidth="27920" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId3"/>
+    <pivotCache cacheId="7" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -184,7 +184,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -197,14 +197,14 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" altLang="zh-TW" sz="1800">
+              <a:rPr lang="en-US" altLang="zh-TW" sz="3200">
                 <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
                 <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
               </a:rPr>
               <a:t>A7</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="zh-TW" altLang="en-US" sz="1800">
+              <a:rPr lang="zh-TW" altLang="en-US" sz="3200">
                 <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
                 <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
               </a:rPr>
@@ -226,7 +226,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -275,7 +275,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -305,7 +305,7 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -332,7 +332,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -392,7 +392,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -452,7 +452,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -512,7 +512,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -572,7 +572,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -632,7 +632,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -692,7 +692,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -752,7 +752,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -849,6 +849,66 @@
             <a:sp3d/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-3B84-664B-AD7F-D7AC0186EA5E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000008-3B84-664B-AD7F-D7AC0186EA5E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-3B84-664B-AD7F-D7AC0186EA5E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
@@ -927,7 +987,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
@@ -1038,6 +1098,86 @@
             <a:sp3d/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-3B84-664B-AD7F-D7AC0186EA5E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-3B84-664B-AD7F-D7AC0186EA5E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000006-3B84-664B-AD7F-D7AC0186EA5E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-3B84-664B-AD7F-D7AC0186EA5E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
@@ -1137,7 +1277,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
@@ -1263,7 +1403,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1336,7 +1476,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -1437,7 +1577,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1450,14 +1590,14 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" altLang="zh-TW" sz="1800">
+              <a:rPr lang="en-US" altLang="zh-TW" sz="3200">
                 <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
                 <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
               </a:rPr>
               <a:t>A7</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="zh-TW" altLang="en-US" sz="1800">
+              <a:rPr lang="zh-TW" altLang="en-US" sz="3200">
                 <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
                 <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
               </a:rPr>
@@ -1479,7 +1619,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -1528,7 +1668,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -1558,7 +1698,7 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -1585,7 +1725,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -1645,7 +1785,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -1705,7 +1845,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -1765,7 +1905,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -1825,7 +1965,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -1885,7 +2025,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -1945,7 +2085,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -2005,7 +2145,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -2065,7 +2205,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -2162,6 +2302,86 @@
             <a:sp3d/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-4C39-434A-B084-4765ABA36222}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000008-4C39-434A-B084-4765ABA36222}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-4C39-434A-B084-4765ABA36222}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000A-4C39-434A-B084-4765ABA36222}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
@@ -2261,7 +2481,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
@@ -2375,6 +2595,86 @@
             <a:sp3d/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-4C39-434A-B084-4765ABA36222}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-4C39-434A-B084-4765ABA36222}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-4C39-434A-B084-4765ABA36222}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000006-4C39-434A-B084-4765ABA36222}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
@@ -2474,7 +2774,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
@@ -2600,7 +2900,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2673,7 +2973,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -3821,15 +4121,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>635000</xdr:colOff>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3857,15 +4157,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>711200</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:colOff>749300</xdr:colOff>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4216,7 +4516,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5B129564-5EDA-3B47-9E02-3F6419FDACAB}" name="樞紐分析表2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5B129564-5EDA-3B47-9E02-3F6419FDACAB}" name="樞紐分析表2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A41:D47" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField dataField="1" numFmtId="176" showAll="0">
@@ -4473,7 +4773,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B8B16ED-0FEC-9042-AB04-3AD6FAB95D9D}" name="樞紐分析表1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B8B16ED-0FEC-9042-AB04-3AD6FAB95D9D}" name="樞紐分析表1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:D9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField dataField="1" numFmtId="176" showAll="0">

--- a/file/XLK-227-A7SignalStrength.xlsx
+++ b/file/XLK-227-A7SignalStrength.xlsx
@@ -8,23 +8,38 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62220CF8-4248-3043-A133-21844D2C5CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4B0EED-5120-1340-BED9-76B83E4CBDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27920" windowHeight="17500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="2" r:id="rId1"/>
     <sheet name="表單回應 1" sheetId="1" r:id="rId2"/>
+    <sheet name="工作表4" sheetId="5" r:id="rId3"/>
+    <sheet name="回應2" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId3"/>
+    <pivotCache cacheId="31" r:id="rId5"/>
+    <pivotCache cacheId="40" r:id="rId6"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="77">
   <si>
     <t>時間戳記</t>
   </si>
@@ -82,15 +97,207 @@
   <si>
     <t>計數 - 時間戳記</t>
   </si>
+  <si>
+    <t>2022/5/10 下午 5:08:50</t>
+  </si>
+  <si>
+    <t>2022/5/10 下午 5:35:39</t>
+  </si>
+  <si>
+    <t>2022/5/10 下午 6:47:49</t>
+  </si>
+  <si>
+    <t>2022/5/10 下午 6:58:17</t>
+  </si>
+  <si>
+    <t>2022/5/10 下午 6:58:53</t>
+  </si>
+  <si>
+    <t>5 格</t>
+  </si>
+  <si>
+    <t>2022/5/10 下午 8:08:59</t>
+  </si>
+  <si>
+    <t>2022/5/10 下午 8:30:19</t>
+  </si>
+  <si>
+    <t>4 - 5 格</t>
+  </si>
+  <si>
+    <t>2022/5/10 下午 8:31:28</t>
+  </si>
+  <si>
+    <t>2022/5/10 下午 10:47:51</t>
+  </si>
+  <si>
+    <t>2022/5/11 上午 12:33:34</t>
+  </si>
+  <si>
+    <t>2022/5/11 上午 1:05:53</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 6:04:09</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 6:48:18</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 6:53:03</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 7:19:23</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 7:33:09</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 7:38:57</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 7:45:03</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 7:50:45</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 7:51:01</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 7:56:35</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 7:57:04</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 8:04:37</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 8:17:34</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 8:18:56</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 8:44:26</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 8:53:03</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 8:59:32</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 9:19:27</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 9:21:40</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 9:30:30</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 10:50:42</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 10:58:29</t>
+  </si>
+  <si>
+    <t>2022/5/10 上午 11:29:28</t>
+  </si>
+  <si>
+    <t>2022/5/10 下午 12:25:45</t>
+  </si>
+  <si>
+    <t>2022/5/10 下午 12:28:17</t>
+  </si>
+  <si>
+    <t>2022/5/10 下午 12:52:49</t>
+  </si>
+  <si>
+    <t>2022/5/10 下午 1:35:06</t>
+  </si>
+  <si>
+    <t>2022/5/10 下午 1:40:13</t>
+  </si>
+  <si>
+    <t>2022/5/10 下午 4:13:29</t>
+  </si>
+  <si>
+    <t>2022/5/10 下午 4:33:05</t>
+  </si>
+  <si>
+    <t>2022/5/10 下午 4:38:23</t>
+  </si>
+  <si>
+    <t>2022/5/10 下午 4:57:15</t>
+  </si>
+  <si>
+    <t>時間</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>區域</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>運營商</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>信號強度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>滿意度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>樂善國小區</t>
+  </si>
+  <si>
+    <t>中心商業區</t>
+  </si>
+  <si>
+    <t>合宜住宅區</t>
+  </si>
+  <si>
+    <t>文青國小區</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">0 - 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+      </rPr>
+      <t>格</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0 - 1 格</t>
+  </si>
+  <si>
+    <t>計數 - 時間</t>
+  </si>
+  <si>
+    <t>平均值 - 滿意度</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="m/d/yyyy\ h:mm:ss"/>
+    <numFmt numFmtId="181" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -110,6 +317,19 @@
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="PMingLiU"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -132,16 +352,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1349,7 +1570,7 @@
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>3</c:v>
@@ -2306,16 +2527,6 @@
             <c:idx val="0"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
-            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000007-4C39-434A-B084-4765ABA36222}"/>
@@ -2326,16 +2537,6 @@
             <c:idx val="1"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
-            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000008-4C39-434A-B084-4765ABA36222}"/>
@@ -2346,16 +2547,6 @@
             <c:idx val="2"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
-            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000009-4C39-434A-B084-4765ABA36222}"/>
@@ -2366,16 +2557,6 @@
             <c:idx val="3"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
-            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000000A-4C39-434A-B084-4765ABA36222}"/>
@@ -2599,16 +2780,6 @@
             <c:idx val="0"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
-            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000003-4C39-434A-B084-4765ABA36222}"/>
@@ -2619,16 +2790,6 @@
             <c:idx val="1"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
-            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000004-4C39-434A-B084-4765ABA36222}"/>
@@ -2639,16 +2800,6 @@
             <c:idx val="2"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
-            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000005-4C39-434A-B084-4765ABA36222}"/>
@@ -2659,16 +2810,6 @@
             <c:idx val="3"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
-            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000006-4C39-434A-B084-4765ABA36222}"/>
@@ -2852,7 +2993,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3049,6 +3190,1038 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[XLK-227-A7SignalStrength.xlsx]工作表4!樞紐分析表4</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="3200">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>A7</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="3200">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>重劃區 手機信號強度 調查 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="3200">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>2022/05/10</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="3200">
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3">
+              <a:lumMod val="40000"/>
+              <a:lumOff val="60000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3">
+              <a:lumMod val="40000"/>
+              <a:lumOff val="60000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3">
+              <a:lumMod val="40000"/>
+              <a:lumOff val="60000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表4!$B$3:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0 - 1 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表4!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中心商業區</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>文青國小區</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>合宜住宅區</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>樂善國小區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表4!$B$5:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F12E-2F44-B9E8-F209B2029BFB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表4!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1 - 2 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表4!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中心商業區</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>文青國小區</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>合宜住宅區</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>樂善國小區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表4!$C$5:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F12E-2F44-B9E8-F209B2029BFB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表4!$D$3:$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4 - 5 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表4!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中心商業區</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>文青國小區</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>合宜住宅區</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>樂善國小區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表4!$D$5:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-F12E-2F44-B9E8-F209B2029BFB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表4!$E$3:$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表4!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中心商業區</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>文青國小區</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>合宜住宅區</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>樂善國小區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表4!$E$5:$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-F12E-2F44-B9E8-F209B2029BFB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="95"/>
+        <c:overlap val="100"/>
+        <c:axId val="1093218384"/>
+        <c:axId val="422991855"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1093218384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="422991855"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="422991855"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1093218384"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -3096,6 +4269,43 @@
   <a:schemeClr val="accent3"/>
   <a:schemeClr val="accent4"/>
   <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
   <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
@@ -4117,20 +5327,525 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>723900</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>635000</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>736600</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4157,16 +5872,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>749300</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4194,49 +5909,55 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="圖表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F19D6A6-8D5D-2D6F-A76D-D20CB6783EBB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="44691.767869328702" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="34" xr:uid="{88C8A250-AC68-4445-979F-920771222576}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="44692.165328703704" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="33" xr:uid="{88C8A250-AC68-4445-979F-920771222576}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:E35" sheet="表單回應 1"/>
+    <worksheetSource ref="A1:E34" sheet="表單回應 1"/>
   </cacheSource>
   <cacheFields count="5">
-    <cacheField name="時間戳記" numFmtId="176">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2022-05-10T06:04:09" maxDate="2022-05-10T17:35:39" count="34">
-        <d v="2022-05-10T06:04:09"/>
-        <d v="2022-05-10T06:48:18"/>
-        <d v="2022-05-10T06:53:03"/>
-        <d v="2022-05-10T07:19:23"/>
-        <d v="2022-05-10T07:33:09"/>
-        <d v="2022-05-10T07:38:57"/>
-        <d v="2022-05-10T07:45:03"/>
-        <d v="2022-05-10T07:50:45"/>
-        <d v="2022-05-10T07:51:01"/>
-        <d v="2022-05-10T07:56:35"/>
-        <d v="2022-05-10T07:57:04"/>
-        <d v="2022-05-10T08:04:37"/>
-        <d v="2022-05-10T08:17:34"/>
-        <d v="2022-05-10T08:18:56"/>
-        <d v="2022-05-10T08:44:26"/>
-        <d v="2022-05-10T08:53:03"/>
-        <d v="2022-05-10T08:59:32"/>
-        <d v="2022-05-10T09:19:27"/>
-        <d v="2022-05-10T09:21:40"/>
-        <d v="2022-05-10T09:30:30"/>
-        <d v="2022-05-10T10:50:42"/>
-        <d v="2022-05-10T10:58:29"/>
-        <d v="2022-05-10T11:29:28"/>
-        <d v="2022-05-10T12:25:45"/>
-        <d v="2022-05-10T12:28:17"/>
-        <d v="2022-05-10T12:52:49"/>
-        <d v="2022-05-10T13:35:06"/>
-        <d v="2022-05-10T13:40:13"/>
-        <d v="2022-05-10T16:13:29"/>
-        <d v="2022-05-10T16:33:05"/>
-        <d v="2022-05-10T16:38:23"/>
-        <d v="2022-05-10T16:57:15"/>
-        <d v="2022-05-10T17:08:50"/>
-        <d v="2022-05-10T17:35:39"/>
-      </sharedItems>
+    <cacheField name="時間戳記" numFmtId="0">
+      <sharedItems/>
     </cacheField>
     <cacheField name="用戶所在區域" numFmtId="0">
       <sharedItems count="4">
@@ -4272,292 +5993,851 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="44692.16566770833" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="43" xr:uid="{ADBD2CDB-B673-2B4E-AF52-6FFC9A7F2327}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:E44" sheet="回應2"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="時間" numFmtId="0">
+      <sharedItems count="43">
+        <s v="2022/5/10 上午 6:04:09"/>
+        <s v="2022/5/10 上午 6:48:18"/>
+        <s v="2022/5/10 上午 6:53:03"/>
+        <s v="2022/5/10 上午 7:19:23"/>
+        <s v="2022/5/10 上午 7:33:09"/>
+        <s v="2022/5/10 上午 7:38:57"/>
+        <s v="2022/5/10 上午 7:45:03"/>
+        <s v="2022/5/10 上午 7:50:45"/>
+        <s v="2022/5/10 上午 7:51:01"/>
+        <s v="2022/5/10 上午 7:56:35"/>
+        <s v="2022/5/10 上午 7:57:04"/>
+        <s v="2022/5/10 上午 8:04:37"/>
+        <s v="2022/5/10 上午 8:17:34"/>
+        <s v="2022/5/10 上午 8:18:56"/>
+        <s v="2022/5/10 上午 8:44:26"/>
+        <s v="2022/5/10 上午 8:53:03"/>
+        <s v="2022/5/10 上午 8:59:32"/>
+        <s v="2022/5/10 上午 9:19:27"/>
+        <s v="2022/5/10 上午 9:21:40"/>
+        <s v="2022/5/10 上午 9:30:30"/>
+        <s v="2022/5/10 上午 10:50:42"/>
+        <s v="2022/5/10 上午 10:58:29"/>
+        <s v="2022/5/10 上午 11:29:28"/>
+        <s v="2022/5/10 下午 12:25:45"/>
+        <s v="2022/5/10 下午 12:28:17"/>
+        <s v="2022/5/10 下午 12:52:49"/>
+        <s v="2022/5/10 下午 1:35:06"/>
+        <s v="2022/5/10 下午 1:40:13"/>
+        <s v="2022/5/10 下午 4:13:29"/>
+        <s v="2022/5/10 下午 4:33:05"/>
+        <s v="2022/5/10 下午 4:38:23"/>
+        <s v="2022/5/10 下午 4:57:15"/>
+        <s v="2022/5/10 下午 5:08:50"/>
+        <s v="2022/5/10 下午 5:35:39"/>
+        <s v="2022/5/10 下午 6:47:49"/>
+        <s v="2022/5/10 下午 6:58:17"/>
+        <s v="2022/5/10 下午 6:58:53"/>
+        <s v="2022/5/10 下午 8:08:59"/>
+        <s v="2022/5/10 下午 8:30:19"/>
+        <s v="2022/5/10 下午 8:31:28"/>
+        <s v="2022/5/10 下午 10:47:51"/>
+        <s v="2022/5/11 上午 12:33:34"/>
+        <s v="2022/5/11 上午 1:05:53"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="區域" numFmtId="0">
+      <sharedItems count="4">
+        <s v="樂善國小區"/>
+        <s v="中心商業區"/>
+        <s v="合宜住宅區"/>
+        <s v="文青國小區"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="運營商" numFmtId="0">
+      <sharedItems count="4">
+        <s v="中華電信"/>
+        <s v="遠傳電信"/>
+        <s v="台灣之星"/>
+        <s v="台灣大哥大"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="信號強度" numFmtId="0">
+      <sharedItems count="4">
+        <s v="0 - 1 格"/>
+        <s v="1 - 2 格"/>
+        <s v="5 格"/>
+        <s v="4 - 5 格"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="滿意度" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5" count="4">
+        <n v="1"/>
+        <n v="2"/>
+        <n v="3"/>
+        <n v="5"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="34">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="33">
   <r>
-    <x v="0"/>
+    <s v="2022/5/10 上午 6:04:09"/>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 6:48:18"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 6:53:03"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 7:19:23"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 7:33:09"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 7:38:57"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 7:45:03"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 7:50:45"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 7:51:01"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 7:56:35"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 7:57:04"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 8:04:37"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 8:17:34"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 8:18:56"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 8:44:26"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 8:53:03"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 8:59:32"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 9:19:27"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 9:21:40"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 9:30:30"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 10:50:42"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 10:58:29"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 上午 11:29:28"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 下午 12:25:45"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 下午 12:28:17"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 下午 12:52:49"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 下午 1:35:06"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 下午 1:40:13"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="2022/5/10 下午 4:13:29"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 下午 4:33:05"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 下午 4:38:23"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="2022/5/10 下午 4:57:15"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="2022/5/10 下午 5:08:50"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="43">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="1"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="3"/>
     <x v="0"/>
     <x v="0"/>
     <x v="1"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="4"/>
     <x v="3"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="5"/>
     <x v="1"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="6"/>
     <x v="2"/>
     <x v="2"/>
     <x v="1"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="7"/>
     <x v="1"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="8"/>
     <x v="1"/>
     <x v="1"/>
     <x v="1"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="9"/>
     <x v="0"/>
     <x v="1"/>
     <x v="1"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="10"/>
     <x v="3"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="11"/>
     <x v="1"/>
     <x v="2"/>
     <x v="1"/>
-    <n v="3"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="12"/>
     <x v="0"/>
     <x v="3"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="13"/>
     <x v="1"/>
     <x v="3"/>
     <x v="1"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="14"/>
     <x v="0"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="15"/>
     <x v="2"/>
     <x v="3"/>
     <x v="1"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="16"/>
     <x v="1"/>
     <x v="1"/>
     <x v="1"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="17"/>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="18"/>
     <x v="2"/>
     <x v="3"/>
     <x v="1"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="19"/>
     <x v="2"/>
     <x v="0"/>
     <x v="1"/>
-    <n v="3"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="20"/>
     <x v="0"/>
     <x v="3"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="21"/>
     <x v="1"/>
     <x v="3"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="22"/>
     <x v="2"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="23"/>
     <x v="0"/>
     <x v="3"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="24"/>
     <x v="2"/>
     <x v="0"/>
     <x v="1"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="25"/>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="26"/>
     <x v="0"/>
     <x v="3"/>
     <x v="1"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="27"/>
     <x v="2"/>
     <x v="1"/>
     <x v="1"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="28"/>
     <x v="1"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="29"/>
     <x v="1"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="30"/>
     <x v="2"/>
     <x v="1"/>
     <x v="1"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="31"/>
     <x v="2"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="32"/>
     <x v="3"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="33"/>
     <x v="3"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="39"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="41"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="42"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5B129564-5EDA-3B47-9E02-3F6419FDACAB}" name="樞紐分析表2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="A41:D47" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B8B16ED-0FEC-9042-AB04-3AD6FAB95D9D}" name="樞紐分析表1" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="A3:D9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
-    <pivotField dataField="1" numFmtId="176" showAll="0">
-      <items count="35">
+    <pivotField dataField="1" numFmtId="176" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="3"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="計數 - 時間戳記" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="9">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5B129564-5EDA-3B47-9E02-3F6419FDACAB}" name="樞紐分析表2" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="A41:D47" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField dataField="1" numFmtId="176" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="5">
@@ -4772,12 +7052,79 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B8B16ED-0FEC-9042-AB04-3AD6FAB95D9D}" name="樞紐分析表1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="A3:D9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C39C3B49-0642-CA4E-B971-F21D8BC671F8}" name="樞紐分析表6" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A90:B95" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
-    <pivotField dataField="1" numFmtId="176" showAll="0">
-      <items count="35">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="平均值 - 滿意度" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="181"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{74C291C8-A570-2643-9FA5-76DCD860F47A}" name="樞紐分析表5" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A46:F52" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField dataField="1" showAll="0">
+      <items count="44">
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -4798,20 +7145,154 @@
         <item x="17"/>
         <item x="18"/>
         <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="40"/>
         <item x="23"/>
         <item x="24"/>
         <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
         <item x="28"/>
         <item x="29"/>
         <item x="30"/>
         <item x="31"/>
         <item x="32"/>
         <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="42"/>
+        <item x="41"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="3"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="計數 - 時間" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{467A7650-3AB5-A64B-AD8A-6CAA0841DDB0}" name="樞紐分析表4" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:F9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField dataField="1" showAll="0">
+      <items count="44">
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="40"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="42"/>
+        <item x="41"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -4826,9 +7307,11 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
-      <items count="3">
+      <items count="5">
+        <item x="0"/>
         <item x="1"/>
-        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -4857,21 +7340,27 @@
   <colFields count="1">
     <field x="3"/>
   </colFields>
-  <colItems count="3">
+  <colItems count="5">
     <i>
       <x/>
     </i>
     <i>
       <x v="1"/>
     </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="計數 - 時間戳記" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="計數 - 時間" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="9">
+  <chartFormats count="6">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
@@ -4896,32 +7385,26 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="0" format="2">
+    <chartFormat chart="0" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
+        <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="0"/>
-          </reference>
           <reference field="3" count="1" selected="0">
-            <x v="1"/>
+            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="0" format="3">
+    <chartFormat chart="0" format="3" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
+        <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="1"/>
-          </reference>
           <reference field="3" count="1" selected="0">
-            <x v="1"/>
+            <x v="3"/>
           </reference>
         </references>
       </pivotArea>
@@ -4933,7 +7416,7 @@
             <x v="0"/>
           </reference>
           <reference field="1" count="1" selected="0">
-            <x v="3"/>
+            <x v="0"/>
           </reference>
           <reference field="3" count="1" selected="0">
             <x v="1"/>
@@ -4952,51 +7435,6 @@
           </reference>
           <reference field="3" count="1" selected="0">
             <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -5222,15 +7660,15 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B4" t="s">
@@ -5244,83 +7682,83 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>5</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>5</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6">
-        <v>4</v>
-      </c>
-      <c r="D6" s="6">
-        <v>4</v>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4">
+        <v>3</v>
+      </c>
+      <c r="D6" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="4">
         <v>7</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <v>3</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="4">
         <v>3</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
         <v>7</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <v>15</v>
       </c>
-      <c r="C9" s="6">
-        <v>19</v>
-      </c>
-      <c r="D9" s="6">
-        <v>34</v>
+      <c r="C9" s="4">
+        <v>18</v>
+      </c>
+      <c r="D9" s="4">
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B42" t="s">
@@ -5334,73 +7772,73 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B43" s="4">
         <v>4</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="4">
         <v>9</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B44" s="6">
+      <c r="B44" s="4">
         <v>4</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="4">
         <v>4</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="4">
         <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="6">
+      <c r="B45" s="4">
         <v>2</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="4">
         <v>2</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="6">
+      <c r="B46" s="4">
         <v>5</v>
       </c>
-      <c r="C46" s="6">
-        <v>4</v>
-      </c>
-      <c r="D46" s="6">
-        <v>9</v>
+      <c r="C46" s="4">
+        <v>3</v>
+      </c>
+      <c r="D46" s="4">
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="4">
         <v>15</v>
       </c>
-      <c r="C47" s="6">
-        <v>19</v>
-      </c>
-      <c r="D47" s="6">
-        <v>34</v>
+      <c r="C47" s="4">
+        <v>18</v>
+      </c>
+      <c r="D47" s="4">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -5415,10 +7853,12 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="11" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="26.1640625" customWidth="1"/>
+    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="3" max="11" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5439,580 +7879,1794 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="2">
-        <v>44691.252881203705</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="2">
-        <v>44691.283536331015</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="2">
-        <v>44691.286845844908</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="2">
-        <v>44691.305132928246</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="2">
-        <v>44691.314691400461</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="2">
-        <v>44691.318718356481</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="2">
-        <v>44691.322956099539</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="2">
-        <v>44691.32690586806</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="2">
-        <v>44691.327100497685</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="2">
-        <v>44691.330955717596</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="2">
-        <v>44691.331296666671</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="2">
-        <v>44691.336538819443</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="2">
-        <v>44691.345530983795</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="2">
-        <v>44691.346478009262</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="2">
-        <v>44691.364191365741</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="A16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="2">
-        <v>44691.370168124995</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="A17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="2">
-        <v>44691.374681041663</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="A18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="2">
-        <v>44691.388505300929</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="A19" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="2">
-        <v>44691.390042268518</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="A20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="2">
-        <v>44691.396184108795</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="A21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="2">
-        <v>44691.451873043981</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="A22" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="2">
-        <v>44691.457282928241</v>
-      </c>
-      <c r="B23" s="3" t="s">
+      <c r="A23" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="2">
-        <v>44691.478792048612</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="A24" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="2">
-        <v>44691.517881747684</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="A25" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="2">
-        <v>44691.519640879633</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="A26" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="2">
-        <v>44691.536673553244</v>
-      </c>
-      <c r="B27" s="3" t="s">
+      <c r="A27" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="2">
-        <v>44691.566039120371</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="A28" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="2">
-        <v>44691.569596655092</v>
-      </c>
-      <c r="B29" s="3" t="s">
+      <c r="A29" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="2">
-        <v>44691.676027071764</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="A30" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="2">
-        <v>44691.689639432865</v>
-      </c>
-      <c r="B31" s="3" t="s">
+      <c r="A31" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="2">
-        <v>44691.693325266198</v>
-      </c>
-      <c r="B32" s="3" t="s">
+      <c r="A32" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="2">
-        <v>44691.706419259259</v>
-      </c>
-      <c r="B33" s="3" t="s">
+      <c r="A33" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="2">
-        <v>44691.714463460652</v>
-      </c>
-      <c r="B34" s="3" t="s">
+      <c r="A34" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="2">
-        <v>44691.733091145834</v>
-      </c>
-      <c r="B35" s="3" t="s">
+      <c r="A35" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E40" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF202991-6702-9149-BD37-B4BDBAB7FA46}">
+  <dimension ref="A3:F95"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="4">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="4">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="4">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4">
+        <v>9</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="4">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="4">
+        <v>22</v>
+      </c>
+      <c r="C9" s="4">
+        <v>19</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A46" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>74</v>
+      </c>
+      <c r="C47" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" t="s">
+        <v>27</v>
+      </c>
+      <c r="E47" t="s">
+        <v>24</v>
+      </c>
+      <c r="F47" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="4">
+        <v>11</v>
+      </c>
+      <c r="C48" s="4">
+        <v>7</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A49" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" s="4">
+        <v>4</v>
+      </c>
+      <c r="C49" s="4">
+        <v>5</v>
+      </c>
+      <c r="D49" s="4">
+        <v>1</v>
+      </c>
+      <c r="E49" s="4">
+        <v>1</v>
+      </c>
+      <c r="F49" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50" s="4">
+        <v>3</v>
+      </c>
+      <c r="C50" s="4">
+        <v>2</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="4">
+        <v>4</v>
+      </c>
+      <c r="C51" s="4">
+        <v>5</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B52" s="4">
+        <v>22</v>
+      </c>
+      <c r="C52" s="4">
+        <v>19</v>
+      </c>
+      <c r="D52" s="4">
+        <v>1</v>
+      </c>
+      <c r="E52" s="4">
+        <v>1</v>
+      </c>
+      <c r="F52" s="4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A91" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B91" s="7">
+        <v>1.2222222222222223</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A92" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B92" s="7">
+        <v>1.9090909090909092</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A93" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B93" s="7">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A94" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B94" s="7">
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A95" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B95" s="7">
+        <v>1.4651162790697674</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BABFF738-CD62-FB44-9EA7-8FFE49CE3087}">
+  <dimension ref="A1:E44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="36.1640625" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A1" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A22" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A23" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A24" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A25" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A26" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A27" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A28" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A29" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A30" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E30" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A31" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A32" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A33" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A34" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E34" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A35" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E35" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A37" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A38" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A39" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A40" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E40" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A41" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A42" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E42" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A43" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E43" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="5">
         <v>1</v>
       </c>
     </row>

--- a/file/XLK-227-A7SignalStrength.xlsx
+++ b/file/XLK-227-A7SignalStrength.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4B0EED-5120-1340-BED9-76B83E4CBDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552EF376-0657-7B4E-89B9-7AE2953AFCD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="27920" windowHeight="17500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3660" yWindow="1400" windowWidth="27920" windowHeight="17500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="2" r:id="rId1"/>
@@ -4222,6 +4222,1490 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[XLK-227-A7SignalStrength.xlsx]工作表4!樞紐分析表5</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="3200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>電信業</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="zh-TW" sz="3200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t> 手機信號強度 調查 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="3200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>2022/05/10</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="zh-TW" sz="3200">
+              <a:effectLst/>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表4!$B$46:$B$47</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0 - 1 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表4!$A$48:$A$52</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中華電信</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>台灣大哥大</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>台灣之星</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>遠傳電信</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表4!$B$48:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-48EB-604C-B6E1-5D562710C60B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表4!$C$46:$C$47</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1 - 2 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表4!$A$48:$A$52</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中華電信</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>台灣大哥大</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>台灣之星</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>遠傳電信</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表4!$C$48:$C$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-48EB-604C-B6E1-5D562710C60B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表4!$D$46:$D$47</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4 - 5 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表4!$A$48:$A$52</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中華電信</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>台灣大哥大</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>台灣之星</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>遠傳電信</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表4!$D$48:$D$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-48EB-604C-B6E1-5D562710C60B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表4!$E$46:$E$47</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表4!$A$48:$A$52</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中華電信</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>台灣大哥大</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>台灣之星</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>遠傳電信</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表4!$E$48:$E$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-48EB-604C-B6E1-5D562710C60B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="95"/>
+        <c:overlap val="100"/>
+        <c:axId val="1566812848"/>
+        <c:axId val="1336272048"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1566812848"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1336272048"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1336272048"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1566812848"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[XLK-227-A7SignalStrength.xlsx]工作表4!樞紐分析表6</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="zh-TW" sz="3200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>電信業 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="3200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>滿意度 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="zh-TW" sz="3200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>調查 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="3200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>2022/05/10</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="3200">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="2800" b="0" i="0" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>滿分 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="2800" b="0" i="0" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>5</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="zh-TW" sz="2800">
+              <a:effectLst/>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表4!$B$90</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>合計</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表4!$A$91:$A$95</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中華電信</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>台灣大哥大</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>台灣之星</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>遠傳電信</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表4!$B$91:$B$95</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00_ </c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.2222222222222223</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.9090909090909092</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3333333333333333</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C031-064C-9474-A4C7319E8F4D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="-25"/>
+        <c:axId val="259880655"/>
+        <c:axId val="1341015456"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="259880655"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1341015456"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1341015456"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="#,##0.00_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="259880655"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -4339,6 +5823,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
   <cs:axisTitle>
@@ -5800,6 +7364,1014 @@
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -5942,6 +8514,78 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="圖表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFAC6A08-F215-EF10-44B9-C6A98A7D1C71}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="圖表 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E71989CE-5B77-19E1-0E1A-7D497C7D31F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -7053,7 +9697,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C39C3B49-0642-CA4E-B971-F21D8BC671F8}" name="樞紐分析表6" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C39C3B49-0642-CA4E-B971-F21D8BC671F8}" name="樞紐分析表6" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A90:B95" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0"/>
@@ -7104,6 +9748,17 @@
   <dataFields count="1">
     <dataField name="平均值 - 滿意度" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="181"/>
   </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -7117,7 +9772,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{74C291C8-A570-2643-9FA5-76DCD860F47A}" name="樞紐分析表5" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{74C291C8-A570-2643-9FA5-76DCD860F47A}" name="樞紐分析表5" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A46:F52" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField dataField="1" showAll="0">
@@ -7232,6 +9887,56 @@
   <dataFields count="1">
     <dataField name="計數 - 時間" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -7245,7 +9950,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{467A7650-3AB5-A64B-AD8A-6CAA0841DDB0}" name="樞紐分析表4" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{467A7650-3AB5-A64B-AD8A-6CAA0841DDB0}" name="樞紐分析表4" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:F9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField dataField="1" showAll="0">

--- a/file/XLK-227-A7SignalStrength.xlsx
+++ b/file/XLK-227-A7SignalStrength.xlsx
@@ -1,27 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10507"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552EF376-0657-7B4E-89B9-7AE2953AFCD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D6A654-55F9-7845-A1FF-702AE38F7F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3660" yWindow="1400" windowWidth="27920" windowHeight="17500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="500" windowWidth="27920" windowHeight="17500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="2" r:id="rId1"/>
     <sheet name="表單回應 1" sheetId="1" r:id="rId2"/>
     <sheet name="工作表4" sheetId="5" r:id="rId3"/>
     <sheet name="回應2" sheetId="3" r:id="rId4"/>
+    <sheet name="回應3" sheetId="6" r:id="rId5"/>
+    <sheet name="工作表3" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="31" r:id="rId5"/>
-    <pivotCache cacheId="40" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="1" r:id="rId8"/>
+    <pivotCache cacheId="10" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="99">
   <si>
     <t>時間戳記</t>
   </si>
@@ -288,6 +291,76 @@
   <si>
     <t>平均值 - 滿意度</t>
   </si>
+  <si>
+    <t>2022/5/11 上午 7:19:28</t>
+  </si>
+  <si>
+    <t>2022/5/11 上午 7:54:25</t>
+  </si>
+  <si>
+    <t>3 - 4 格</t>
+  </si>
+  <si>
+    <t>2022/5/11 上午 8:43:45</t>
+  </si>
+  <si>
+    <t>2022/5/11 上午 8:55:55</t>
+  </si>
+  <si>
+    <t>2022/5/11 下午 12:11:43</t>
+  </si>
+  <si>
+    <t>2022/5/11 下午 12:21:14</t>
+  </si>
+  <si>
+    <t>2022/5/11 下午 2:14:05</t>
+  </si>
+  <si>
+    <t>2022/5/11 下午 3:11:43</t>
+  </si>
+  <si>
+    <t>2022/5/12 上午 6:46:14</t>
+  </si>
+  <si>
+    <t>2022/5/12 上午 7:31:51</t>
+  </si>
+  <si>
+    <t>2022/5/12 上午 11:23:30</t>
+  </si>
+  <si>
+    <t>2022/5/12 下午 12:11:32</t>
+  </si>
+  <si>
+    <t>2022/5/12 下午 4:22:03</t>
+  </si>
+  <si>
+    <t>2022/5/12 下午 9:28:33</t>
+  </si>
+  <si>
+    <t>2022/5/12 下午 10:14:36</t>
+  </si>
+  <si>
+    <t>2022/5/12 下午 10:27:49</t>
+  </si>
+  <si>
+    <t>2022/5/13 下午 9:15:05</t>
+  </si>
+  <si>
+    <t>中心商業區</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>文青國小區</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合宜住宅區</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>樂善國小區</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -295,7 +368,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="m/d/yyyy\ h:mm:ss"/>
-    <numFmt numFmtId="181" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -362,7 +435,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1074,16 +1147,6 @@
             <c:idx val="0"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
-            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000009-3B84-664B-AD7F-D7AC0186EA5E}"/>
@@ -1094,16 +1157,6 @@
             <c:idx val="2"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
-            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000008-3B84-664B-AD7F-D7AC0186EA5E}"/>
@@ -1114,16 +1167,6 @@
             <c:idx val="3"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
-            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000007-3B84-664B-AD7F-D7AC0186EA5E}"/>
@@ -1323,16 +1366,6 @@
             <c:idx val="0"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
-            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000003-3B84-664B-AD7F-D7AC0186EA5E}"/>
@@ -1343,16 +1376,6 @@
             <c:idx val="1"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
-            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000004-3B84-664B-AD7F-D7AC0186EA5E}"/>
@@ -1363,16 +1386,6 @@
             <c:idx val="2"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
-            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000006-3B84-664B-AD7F-D7AC0186EA5E}"/>
@@ -1383,16 +1396,6 @@
             <c:idx val="3"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
-            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000005-3B84-664B-AD7F-D7AC0186EA5E}"/>
@@ -3405,7 +3408,7 @@
         <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent2"/>
+            <a:schemeClr val="accent6"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -4500,7 +4503,7 @@
         <c:idx val="3"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent4"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -5309,9 +5312,16 @@
           </a:p>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="3200">
+              <a:defRPr sz="3200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
                 <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
                 <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -5706,6 +5716,2865 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[XLK-227-A7SignalStrength.xlsx]工作表3!樞紐分析表1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="2800">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>A7</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="2800" baseline="0">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>重劃區 手機信號強度調查 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="2800" baseline="0">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>2022/05/14</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="2800">
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="00B0F0"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="92D050"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表3!$B$3:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0 - 1 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中心商業區</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>文青國小區</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>合宜住宅區</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>樂善國小區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$B$5:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CD95-B045-A6B6-7939CBAAE2BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表3!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1 - 2 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中心商業區</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>文青國小區</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>合宜住宅區</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>樂善國小區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$C$5:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CD95-B045-A6B6-7939CBAAE2BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表3!$D$3:$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3 - 4 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00B0F0"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中心商業區</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>文青國小區</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>合宜住宅區</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>樂善國小區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$D$5:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-CD95-B045-A6B6-7939CBAAE2BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表3!$E$3:$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4 - 5 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="92D050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中心商業區</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>文青國小區</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>合宜住宅區</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>樂善國小區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$E$5:$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-CD95-B045-A6B6-7939CBAAE2BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表3!$F$3:$F$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00B050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中心商業區</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>文青國小區</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>合宜住宅區</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>樂善國小區</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$F$5:$F$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-CD95-B045-A6B6-7939CBAAE2BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="95"/>
+        <c:overlap val="100"/>
+        <c:axId val="551872736"/>
+        <c:axId val="242682335"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="551872736"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="242682335"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="242682335"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="551872736"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[XLK-227-A7SignalStrength.xlsx]工作表3!樞紐分析表2</c:name>
+    <c:fmtId val="2"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="2800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>電信業 手機信號強度調查 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="2800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>2022/05/14</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="2800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="2800">
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="00B0F0"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="92D050"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表3!$B$54:$B$55</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0 - 1 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$A$56:$A$60</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中華電信</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>台灣大哥大</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>台灣之星</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>遠傳電信</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$B$56:$B$60</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2758-0149-AEDB-05EE0CF73743}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表3!$C$54:$C$55</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1 - 2 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$A$56:$A$60</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中華電信</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>台灣大哥大</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>台灣之星</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>遠傳電信</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$C$56:$C$60</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2758-0149-AEDB-05EE0CF73743}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表3!$D$54:$D$55</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3 - 4 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00B0F0"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$A$56:$A$60</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中華電信</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>台灣大哥大</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>台灣之星</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>遠傳電信</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$D$56:$D$60</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-2758-0149-AEDB-05EE0CF73743}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表3!$E$54:$E$55</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4 - 5 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="92D050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$A$56:$A$60</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中華電信</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>台灣大哥大</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>台灣之星</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>遠傳電信</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$E$56:$E$60</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-2758-0149-AEDB-05EE0CF73743}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表3!$F$54:$F$55</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5 格</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00B050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$A$56:$A$60</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中華電信</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>台灣大哥大</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>台灣之星</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>遠傳電信</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$F$56:$F$60</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-2758-0149-AEDB-05EE0CF73743}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="95"/>
+        <c:overlap val="100"/>
+        <c:axId val="630638000"/>
+        <c:axId val="630834656"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="630638000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="630834656"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="630834656"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="630638000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[XLK-227-A7SignalStrength.xlsx]工作表3!樞紐分析表3</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="zh-TW" sz="2800" b="0" i="0" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>電信業 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="2800" b="0" i="0" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>滿意度</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="zh-TW" sz="2800" b="0" i="0" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>調查 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="2800" b="0" i="0" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>2022/05/14</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2800">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="2800" b="0" i="0" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>滿分</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="2800" b="0" i="0" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>5</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="2800" b="0" i="0" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>分</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="zh-TW" sz="2800" b="0" i="0" baseline="0">
+                <a:effectLst/>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="zh-TW" sz="2800">
+              <a:effectLst/>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表3!$B$99</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>合計</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$A$100:$A$104</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>中華電信</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>台灣大哥大</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>台灣之星</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>遠傳電信</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$B$100:$B$104</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00_ </c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.1851851851851851</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.8333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.8888888888888888</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3333333333333333</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0E2C-CF45-99E8-3F5B2CBAA839}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="-25"/>
+        <c:axId val="1255213952"/>
+        <c:axId val="1255215600"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1255213952"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1255215600"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1255215600"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="#,##0.00_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1255213952"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -5903,6 +8772,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
   <cs:axisTitle>
@@ -7902,6 +10891,1519 @@
 </file>
 
 <file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -8594,6 +13096,119 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="圖表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41E2E18E-FAD6-6351-9478-1E5039024F1D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>368300</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="圖表 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{401A892F-9E47-4284-8330-E425FB8E3E85}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="圖表 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56FB91AD-A48E-28D0-DCFF-9381290B65B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="44692.165328703704" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="33" xr:uid="{88C8A250-AC68-4445-979F-920771222576}">
   <cacheSource type="worksheet">
@@ -8731,6 +13346,118 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="44695.354548379626" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="60" xr:uid="{542465DB-5074-DC4F-BE7F-5A22A040EE05}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:E61" sheet="回應3"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="時間" numFmtId="0">
+      <sharedItems count="60">
+        <s v="2022/5/10 上午 6:48:18"/>
+        <s v="2022/5/10 上午 7:51:01"/>
+        <s v="2022/5/10 上午 8:04:37"/>
+        <s v="2022/5/10 上午 8:18:56"/>
+        <s v="2022/5/10 上午 8:59:32"/>
+        <s v="2022/5/10 下午 6:58:17"/>
+        <s v="2022/5/10 下午 8:08:59"/>
+        <s v="2022/5/11 下午 3:11:43"/>
+        <s v="2022/5/12 下午 4:22:03"/>
+        <s v="2022/5/12 下午 10:14:36"/>
+        <s v="2022/5/12 下午 10:27:49"/>
+        <s v="2022/5/12 下午 12:11:32"/>
+        <s v="2022/5/10 上午 7:38:57"/>
+        <s v="2022/5/10 上午 7:50:45"/>
+        <s v="2022/5/10 上午 10:58:29"/>
+        <s v="2022/5/10 下午 4:13:29"/>
+        <s v="2022/5/10 下午 4:33:05"/>
+        <s v="2022/5/11 上午 7:19:28"/>
+        <s v="2022/5/11 上午 8:43:45"/>
+        <s v="2022/5/11 下午 12:21:14"/>
+        <s v="2022/5/12 上午 6:46:14"/>
+        <s v="2022/5/10 上午 7:33:09"/>
+        <s v="2022/5/10 上午 7:57:04"/>
+        <s v="2022/5/10 下午 5:08:50"/>
+        <s v="2022/5/10 下午 5:35:39"/>
+        <s v="2022/5/13 下午 9:15:05"/>
+        <s v="2022/5/10 上午 7:45:03"/>
+        <s v="2022/5/10 上午 8:53:03"/>
+        <s v="2022/5/10 上午 9:21:40"/>
+        <s v="2022/5/10 上午 9:30:30"/>
+        <s v="2022/5/10 下午 12:28:17"/>
+        <s v="2022/5/10 下午 1:40:13"/>
+        <s v="2022/5/10 下午 4:38:23"/>
+        <s v="2022/5/10 下午 8:31:28"/>
+        <s v="2022/5/11 上午 1:05:53"/>
+        <s v="2022/5/11 上午 7:54:25"/>
+        <s v="2022/5/11 上午 8:55:55"/>
+        <s v="2022/5/10 下午 8:30:19"/>
+        <s v="2022/5/10 上午 6:53:03"/>
+        <s v="2022/5/10 上午 11:29:28"/>
+        <s v="2022/5/10 下午 4:57:15"/>
+        <s v="2022/5/12 上午 11:23:30"/>
+        <s v="2022/5/10 上午 7:19:23"/>
+        <s v="2022/5/10 上午 7:56:35"/>
+        <s v="2022/5/10 下午 1:35:06"/>
+        <s v="2022/5/11 下午 2:14:05"/>
+        <s v="2022/5/10 下午 6:58:53"/>
+        <s v="2022/5/10 上午 6:04:09"/>
+        <s v="2022/5/10 上午 8:17:34"/>
+        <s v="2022/5/10 上午 8:44:26"/>
+        <s v="2022/5/10 上午 9:19:27"/>
+        <s v="2022/5/10 上午 10:50:42"/>
+        <s v="2022/5/10 下午 12:25:45"/>
+        <s v="2022/5/10 下午 12:52:49"/>
+        <s v="2022/5/10 下午 6:47:49"/>
+        <s v="2022/5/10 下午 10:47:51"/>
+        <s v="2022/5/11 上午 12:33:34"/>
+        <s v="2022/5/11 下午 12:11:43"/>
+        <s v="2022/5/12 上午 7:31:51"/>
+        <s v="2022/5/12 下午 9:28:33"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="區域" numFmtId="0">
+      <sharedItems count="4">
+        <s v="中心商業區"/>
+        <s v="文青國小區"/>
+        <s v="合宜住宅區"/>
+        <s v="樂善國小區"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="運營商" numFmtId="0">
+      <sharedItems count="4">
+        <s v="中華電信"/>
+        <s v="遠傳電信"/>
+        <s v="台灣之星"/>
+        <s v="台灣大哥大"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="信號強度" numFmtId="0">
+      <sharedItems count="5">
+        <s v="1 - 2 格"/>
+        <s v="3 - 4 格"/>
+        <s v="0 - 1 格"/>
+        <s v="4 - 5 格"/>
+        <s v="5 格"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="滿意度" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5" count="4">
+        <n v="1"/>
+        <n v="2"/>
+        <n v="3"/>
+        <n v="5"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="33">
   <r>
@@ -9273,8 +14000,433 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="60">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="33"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="39"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="41"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="42"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="43"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="44"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="45"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="46"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="47"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="48"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="49"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="50"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="51"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="52"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="53"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="54"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="55"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="56"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="57"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="58"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="59"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B8B16ED-0FEC-9042-AB04-3AD6FAB95D9D}" name="樞紐分析表1" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B8B16ED-0FEC-9042-AB04-3AD6FAB95D9D}" name="樞紐分析表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:D9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField dataField="1" numFmtId="176" showAll="0"/>
@@ -9478,7 +14630,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5B129564-5EDA-3B47-9E02-3F6419FDACAB}" name="樞紐分析表2" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5B129564-5EDA-3B47-9E02-3F6419FDACAB}" name="樞紐分析表2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A41:D47" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField dataField="1" numFmtId="176" showAll="0"/>
@@ -9697,7 +14849,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C39C3B49-0642-CA4E-B971-F21D8BC671F8}" name="樞紐分析表6" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C39C3B49-0642-CA4E-B971-F21D8BC671F8}" name="樞紐分析表6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A90:B95" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0"/>
@@ -9746,7 +14898,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="平均值 - 滿意度" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="181"/>
+    <dataField name="平均值 - 滿意度" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="177"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="0" format="0" series="1">
@@ -9772,7 +14924,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{74C291C8-A570-2643-9FA5-76DCD860F47A}" name="樞紐分析表5" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{74C291C8-A570-2643-9FA5-76DCD860F47A}" name="樞紐分析表5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A46:F52" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField dataField="1" showAll="0">
@@ -9950,7 +15102,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{467A7650-3AB5-A64B-AD8A-6CAA0841DDB0}" name="樞紐分析表4" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{467A7650-3AB5-A64B-AD8A-6CAA0841DDB0}" name="樞紐分析表4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:F9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField dataField="1" showAll="0">
@@ -10137,6 +15289,578 @@
           </reference>
           <reference field="1" count="1" selected="0">
             <x v="2"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A16A21B5-C4A0-4C4F-A8D5-FA05AABBC0BC}" name="樞紐分析表3" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A99:B104" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="平均值 - 滿意度" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="177"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{190F1A8A-1272-1648-9BF3-9796C199BC39}" name="樞紐分析表2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="A54:G60" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField dataField="1" showAll="0">
+      <items count="61">
+        <item x="51"/>
+        <item x="14"/>
+        <item x="39"/>
+        <item x="47"/>
+        <item x="0"/>
+        <item x="38"/>
+        <item x="42"/>
+        <item x="21"/>
+        <item x="12"/>
+        <item x="26"/>
+        <item x="13"/>
+        <item x="1"/>
+        <item x="43"/>
+        <item x="22"/>
+        <item x="2"/>
+        <item x="48"/>
+        <item x="3"/>
+        <item x="49"/>
+        <item x="27"/>
+        <item x="4"/>
+        <item x="50"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="44"/>
+        <item x="31"/>
+        <item x="55"/>
+        <item x="52"/>
+        <item x="30"/>
+        <item x="53"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="32"/>
+        <item x="40"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="54"/>
+        <item x="5"/>
+        <item x="46"/>
+        <item x="6"/>
+        <item x="37"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="56"/>
+        <item x="17"/>
+        <item x="35"/>
+        <item x="18"/>
+        <item x="36"/>
+        <item x="57"/>
+        <item x="19"/>
+        <item x="45"/>
+        <item x="7"/>
+        <item x="41"/>
+        <item x="20"/>
+        <item x="58"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="8"/>
+        <item x="59"/>
+        <item x="25"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="3"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="計數 - 時間" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="10">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8A989E97-C415-E145-AF52-D8FA03D164AA}" name="樞紐分析表1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:G9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField dataField="1" showAll="0">
+      <items count="61">
+        <item x="51"/>
+        <item x="14"/>
+        <item x="39"/>
+        <item x="47"/>
+        <item x="0"/>
+        <item x="38"/>
+        <item x="42"/>
+        <item x="21"/>
+        <item x="12"/>
+        <item x="26"/>
+        <item x="13"/>
+        <item x="1"/>
+        <item x="43"/>
+        <item x="22"/>
+        <item x="2"/>
+        <item x="48"/>
+        <item x="3"/>
+        <item x="49"/>
+        <item x="27"/>
+        <item x="4"/>
+        <item x="50"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="44"/>
+        <item x="31"/>
+        <item x="55"/>
+        <item x="52"/>
+        <item x="30"/>
+        <item x="53"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="32"/>
+        <item x="40"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="54"/>
+        <item x="5"/>
+        <item x="46"/>
+        <item x="6"/>
+        <item x="37"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="56"/>
+        <item x="17"/>
+        <item x="35"/>
+        <item x="18"/>
+        <item x="36"/>
+        <item x="57"/>
+        <item x="19"/>
+        <item x="45"/>
+        <item x="7"/>
+        <item x="41"/>
+        <item x="20"/>
+        <item x="58"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="8"/>
+        <item x="59"/>
+        <item x="25"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="3"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="計數 - 時間" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
           </reference>
           <reference field="3" count="1" selected="0">
             <x v="1"/>
@@ -10558,7 +16282,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="26.1640625" customWidth="1"/>
@@ -11311,6 +17035,295 @@
         <v>9</v>
       </c>
       <c r="E44" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E48" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E50" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E56" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" s="5">
         <v>1</v>
       </c>
     </row>
@@ -12379,4 +18392,1391 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31A3115-B9E0-CF42-B06D-35D36188C261}">
+  <dimension ref="A1:E61"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="26.1640625" customWidth="1"/>
+    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="3" max="11" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E37" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E39" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E40" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E41" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E42" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E43" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E47" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E49" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E50" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E51" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E52" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E53" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E55" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E56" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E58" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E59" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E60" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E61" s="5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E61">
+    <sortCondition ref="B2:B61"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42117F21-0F60-0D40-A7A6-D3C9FBD66767}">
+  <dimension ref="A3:G104"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="4">
+        <v>8</v>
+      </c>
+      <c r="C5" s="4">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="4">
+        <v>5</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="4">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4">
+        <v>9</v>
+      </c>
+      <c r="D7" s="4">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="4">
+        <v>13</v>
+      </c>
+      <c r="C8" s="4">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="4">
+        <v>30</v>
+      </c>
+      <c r="C9" s="4">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4">
+        <v>2</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A54" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>74</v>
+      </c>
+      <c r="C55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" t="s">
+        <v>79</v>
+      </c>
+      <c r="E55" t="s">
+        <v>27</v>
+      </c>
+      <c r="F55" t="s">
+        <v>24</v>
+      </c>
+      <c r="G55" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A56" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" s="4">
+        <v>15</v>
+      </c>
+      <c r="C56" s="4">
+        <v>10</v>
+      </c>
+      <c r="D56" s="4">
+        <v>2</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A57" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" s="4">
+        <v>5</v>
+      </c>
+      <c r="C57" s="4">
+        <v>5</v>
+      </c>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4">
+        <v>1</v>
+      </c>
+      <c r="F57" s="4">
+        <v>1</v>
+      </c>
+      <c r="G57" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A58" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B58" s="4">
+        <v>4</v>
+      </c>
+      <c r="C58" s="4">
+        <v>3</v>
+      </c>
+      <c r="D58" s="4">
+        <v>1</v>
+      </c>
+      <c r="E58" s="4">
+        <v>1</v>
+      </c>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A59" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" s="4">
+        <v>6</v>
+      </c>
+      <c r="C59" s="4">
+        <v>6</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B60" s="4">
+        <v>30</v>
+      </c>
+      <c r="C60" s="4">
+        <v>24</v>
+      </c>
+      <c r="D60" s="4">
+        <v>3</v>
+      </c>
+      <c r="E60" s="4">
+        <v>2</v>
+      </c>
+      <c r="F60" s="4">
+        <v>1</v>
+      </c>
+      <c r="G60" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A100" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B100" s="7">
+        <v>1.1851851851851851</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A101" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B101" s="7">
+        <v>1.8333333333333333</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A102" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B102" s="7">
+        <v>1.8888888888888888</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A103" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B103" s="7">
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A104" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B104" s="7">
+        <v>1.45</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId4"/>
+</worksheet>
 </file>
--- a/file/XLK-227-A7SignalStrength.xlsx
+++ b/file/XLK-227-A7SignalStrength.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D6A654-55F9-7845-A1FF-702AE38F7F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08189711-A797-EC4C-AC29-C0D98D9AF662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="500" windowWidth="27920" windowHeight="17500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="880" yWindow="1560" windowWidth="27920" windowHeight="17500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="2" r:id="rId1"/>
@@ -15310,7 +15310,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A16A21B5-C4A0-4C4F-A8D5-FA05AABBC0BC}" name="樞紐分析表3" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A16A21B5-C4A0-4C4F-A8D5-FA05AABBC0BC}" name="樞紐分析表3" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A99:B104" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0"/>
@@ -15385,7 +15385,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{190F1A8A-1272-1648-9BF3-9796C199BC39}" name="樞紐分析表2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{190F1A8A-1272-1648-9BF3-9796C199BC39}" name="樞紐分析表2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="A54:G60" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField dataField="1" showAll="0">
@@ -15656,7 +15656,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8A989E97-C415-E145-AF52-D8FA03D164AA}" name="樞紐分析表1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8A989E97-C415-E145-AF52-D8FA03D164AA}" name="樞紐分析表1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:G9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField dataField="1" showAll="0">
